--- a/Export_Vorlage/Haltungen.xlsx
+++ b/Export_Vorlage/Haltungen.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haltungen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haltungen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Haltungen'!$A$26:$AA$5000</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Haltungen'!$25:$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Haltungen'!$26:$26,'Haltungen'!$A:$B</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;CHF&quot; #,##0.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
+    <numFmt numFmtId="166" formatCode="0&quot; Haltungen&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -426,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +527,15 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -817,13 +827,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -843,10 +853,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -863,10 +873,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF6600"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -883,10 +893,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -903,10 +913,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AEB135"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -923,10 +933,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -942,8 +952,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -992,10 +1002,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1004,13 +1014,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1030,10 +1040,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="92D050"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1050,10 +1060,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E7E6E6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1069,8 +1079,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1119,10 +1129,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1131,13 +1141,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1157,10 +1167,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1177,10 +1187,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1197,10 +1207,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF8000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1217,10 +1227,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1237,10 +1247,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1256,8 +1266,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1306,10 +1316,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1318,13 +1328,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1344,10 +1354,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="548235"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1364,10 +1374,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="BF8F00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1384,10 +1394,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00B0F0"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1404,10 +1414,10 @@
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1424,10 +1434,10 @@
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1443,8 +1453,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1493,10 +1503,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1505,13 +1515,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1531,10 +1541,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1551,10 +1561,10 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00B050"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1571,10 +1581,10 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="D6DCE4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
@@ -1590,8 +1600,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="1"/>
               </a:pPr>
@@ -1640,10 +1650,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1652,13 +1662,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1678,17 +1688,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6A6A6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1696,10 +1706,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="3F3F46"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1707,10 +1717,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="808080"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1718,10 +1728,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="FF6600"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1729,10 +1739,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="70AD47"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1740,10 +1750,10 @@
           <dPt>
             <idx val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D6DCE4"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1762,8 +1772,8 @@
         <dLbls>
           <numFmt formatCode="#,##0;-#,##0;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1794,8 +1804,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1824,10 +1834,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1836,13 +1846,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="1"/>
             </a:pPr>
@@ -1862,17 +1872,17 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="548235"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1880,10 +1890,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="FFFF00"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1891,10 +1901,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="FF8000"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1902,10 +1912,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="00B0F0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1913,10 +1923,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1935,8 +1945,8 @@
         <dLbls>
           <numFmt formatCode="#,##0 &quot;CHF&quot;;;&quot;&quot;"/>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="700" b="0"/>
               </a:pPr>
@@ -1967,8 +1977,8 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="700" b="0"/>
             </a:pPr>
@@ -1997,10 +2007,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2009,7 +2019,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="3024000" y="72000"/>
     <ext cx="4680000" cy="558000"/>
@@ -2019,9 +2029,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2036,9 +2046,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2053,9 +2063,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2070,9 +2080,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2087,9 +2097,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2104,9 +2114,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2121,9 +2131,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2138,13 +2148,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2617,7 +2627,7 @@
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="12">
-        <f>COUNTIF($J$27:$J$5000,"0")</f>
+        <f>COUNTIF('Haltungen'!$J$27:$J$5000,"0")</f>
         <v/>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -2626,7 +2636,7 @@
         </is>
       </c>
       <c r="E17" s="12">
-        <f>COUNTIF($O$27:$O$5000,"Abwasser Uri")+COUNTIF($O$27:$O$5000,"AWU")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Abwasser Uri")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU")</f>
         <v/>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -2635,7 +2645,7 @@
         </is>
       </c>
       <c r="G17" s="12">
-        <f>COUNTIF($D$27:$D$5000,"Zement")</f>
+        <f>COUNTIF('Haltungen'!$D$27:$D$5000,"Zement")</f>
         <v/>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -2645,7 +2655,7 @@
       </c>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="12">
-        <f>COUNTIF($K$27:$K$5000,"i.O.")+COUNTIF($K$27:$K$5000,"Prüfung bestanden")+COUNTIF($K$27:$K$5000,"Pruefung bestanden")</f>
+        <f>COUNTIF('Haltungen'!$K$27:$K$5000,"i.O.")+COUNTIF('Haltungen'!$K$27:$K$5000,"Prüfung bestanden")+COUNTIF('Haltungen'!$K$27:$K$5000,"Pruefung bestanden")</f>
         <v/>
       </c>
       <c r="K17" s="15" t="inlineStr">
@@ -2654,7 +2664,7 @@
         </is>
       </c>
       <c r="L17" s="12">
-        <f>COUNTIF($L$27:$L$5000,"Ja")</f>
+        <f>COUNTIF('Haltungen'!$L$27:$L$5000,"Ja")</f>
         <v/>
       </c>
       <c r="M17" s="13" t="inlineStr">
@@ -2663,7 +2673,7 @@
         </is>
       </c>
       <c r="N17" s="12">
-        <f>COUNTIF($P$27:$P$5000,"Abwasser Uri")</f>
+        <f>COUNTIF('Haltungen'!$P$27:$P$5000,"Abwasser Uri")</f>
         <v/>
       </c>
       <c r="O17" s="16" t="inlineStr">
@@ -2674,7 +2684,7 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="17">
-        <f>SUMIF($O$27:$O$5000,"Abwasser Uri",$N$27:$N$5000)+SUMIF($O$27:$O$5000,"AWU",$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Abwasser Uri",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S17" s="16" t="inlineStr">
@@ -2685,7 +2695,7 @@
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n"/>
       <c r="V17" s="18">
-        <f>SUM($S$27:$S$5000)</f>
+        <f>SUM('Haltungen'!$S$27:$S$5000)</f>
         <v/>
       </c>
       <c r="W17" s="2" t="n"/>
@@ -2697,7 +2707,7 @@
         </is>
       </c>
       <c r="AA17" s="12">
-        <f>COUNTIF($Z$27:$Z$5000,"offen")</f>
+        <f>COUNTIF('Haltungen'!$Z$27:$Z$5000,"offen")</f>
         <v/>
       </c>
     </row>
@@ -2709,7 +2719,7 @@
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="12">
-        <f>COUNTIF($J$27:$J$5000,"1")</f>
+        <f>COUNTIF('Haltungen'!$J$27:$J$5000,"1")</f>
         <v/>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -2718,7 +2728,7 @@
         </is>
       </c>
       <c r="E18" s="12">
-        <f>COUNTIF($O$27:$O$5000,"Kanton Uri")+COUNTIF($O$27:$O$5000,"Kanton")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton Uri")+COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton")</f>
         <v/>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -2727,7 +2737,7 @@
         </is>
       </c>
       <c r="G18" s="12">
-        <f>COUNTIF($D$27:$D$5000,"Polyethylen")</f>
+        <f>COUNTIF('Haltungen'!$D$27:$D$5000,"Polyethylen")</f>
         <v/>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -2737,7 +2747,7 @@
       </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="12">
-        <f>COUNTIF($K$27:$K$5000,"beobachten")+COUNTIF($K$27:$K$5000,"Prüfung knapp nicht bestanden")+COUNTIF($K$27:$K$5000,"Pruefung knapp nicht bestanden")</f>
+        <f>COUNTIF('Haltungen'!$K$27:$K$5000,"beobachten")+COUNTIF('Haltungen'!$K$27:$K$5000,"Prüfung knapp nicht bestanden")+COUNTIF('Haltungen'!$K$27:$K$5000,"Pruefung knapp nicht bestanden")</f>
         <v/>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -2746,7 +2756,7 @@
         </is>
       </c>
       <c r="L18" s="12">
-        <f>COUNTIF($L$27:$L$5000,"Nein")</f>
+        <f>COUNTIF('Haltungen'!$L$27:$L$5000,"Nein")</f>
         <v/>
       </c>
       <c r="M18" s="23" t="inlineStr">
@@ -2755,7 +2765,7 @@
         </is>
       </c>
       <c r="N18" s="12">
-        <f>COUNTIF($P$27:$P$5000,"Kanalsanierer")</f>
+        <f>COUNTIF('Haltungen'!$P$27:$P$5000,"Kanalsanierer")</f>
         <v/>
       </c>
       <c r="O18" s="16" t="inlineStr">
@@ -2766,7 +2776,7 @@
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="17">
-        <f>SUMIF($O$27:$O$5000,"Kanton Uri",$N$27:$N$5000)+SUMIF($O$27:$O$5000,"Kanton",$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Kanton Uri",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Kanton",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S18" s="16" t="inlineStr">
@@ -2777,7 +2787,7 @@
       <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="n"/>
       <c r="V18" s="18">
-        <f>SUM($T$27:$T$5000)</f>
+        <f>SUM('Haltungen'!$T$27:$T$5000)</f>
         <v/>
       </c>
       <c r="W18" s="2" t="n"/>
@@ -2789,7 +2799,7 @@
         </is>
       </c>
       <c r="AA18" s="12">
-        <f>COUNTIF($Z$27:$Z$5000,"abgeschlossen")</f>
+        <f>COUNTIF('Haltungen'!$Z$27:$Z$5000,"abgeschlossen")</f>
         <v/>
       </c>
     </row>
@@ -2801,7 +2811,7 @@
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="12">
-        <f>COUNTIF($J$27:$J$5000,"2")</f>
+        <f>COUNTIF('Haltungen'!$J$27:$J$5000,"2")</f>
         <v/>
       </c>
       <c r="D19" s="25" t="inlineStr">
@@ -2810,7 +2820,7 @@
         </is>
       </c>
       <c r="E19" s="12">
-        <f>COUNTIF($O$27:$O$5000,"Bund")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Bund")</f>
         <v/>
       </c>
       <c r="F19" s="26" t="inlineStr">
@@ -2819,7 +2829,7 @@
         </is>
       </c>
       <c r="G19" s="12">
-        <f>COUNTIF($D$27:$D$5000,"Beton")</f>
+        <f>COUNTIF('Haltungen'!$D$27:$D$5000,"Beton")</f>
         <v/>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -2829,7 +2839,7 @@
       </c>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="12">
-        <f>COUNTIF($K$27:$K$5000,"Sanierungsbedarf")+COUNTIF($K$27:$K$5000,"Prüfung nicht bestanden (grob undicht)")+COUNTIF($K$27:$K$5000,"Pruefung nicht bestanden (grob undicht)")</f>
+        <f>COUNTIF('Haltungen'!$K$27:$K$5000,"Sanierungsbedarf")+COUNTIF('Haltungen'!$K$27:$K$5000,"Prüfung nicht bestanden (grob undicht)")+COUNTIF('Haltungen'!$K$27:$K$5000,"Pruefung nicht bestanden (grob undicht)")</f>
         <v/>
       </c>
       <c r="K19" s="5" t="n"/>
@@ -2840,7 +2850,7 @@
         </is>
       </c>
       <c r="N19" s="12">
-        <f>COUNTIF($P$27:$P$5000,"Baumeister")</f>
+        <f>COUNTIF('Haltungen'!$P$27:$P$5000,"Baumeister")</f>
         <v/>
       </c>
       <c r="O19" s="16" t="inlineStr">
@@ -2851,7 +2861,7 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="17">
-        <f>SUMIF($O$27:$O$5000,"Bund",$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Bund",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S19" s="16" t="inlineStr">
@@ -2862,7 +2872,7 @@
       <c r="T19" s="2" t="n"/>
       <c r="U19" s="2" t="n"/>
       <c r="V19" s="18">
-        <f>SUM($U$27:$U$5000)</f>
+        <f>SUM('Haltungen'!$U$27:$U$5000)</f>
         <v/>
       </c>
       <c r="W19" s="2" t="n"/>
@@ -2874,7 +2884,7 @@
         </is>
       </c>
       <c r="AA19" s="12">
-        <f>COUNTA($B$27:$B$5000)-COUNTA($Z$27:$Z$5000)</f>
+        <f>COUNTA('Haltungen'!$B$27:$B$5000)-COUNTA('Haltungen'!$Z$27:$Z$5000)</f>
         <v/>
       </c>
     </row>
@@ -2886,7 +2896,7 @@
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="12">
-        <f>COUNTIF($J$27:$J$5000,"3")</f>
+        <f>COUNTIF('Haltungen'!$J$27:$J$5000,"3")</f>
         <v/>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -2895,7 +2905,7 @@
         </is>
       </c>
       <c r="E20" s="12">
-        <f>COUNTIF($O$27:$O$5000,"Gemeinde")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Gemeinde")</f>
         <v/>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -2904,7 +2914,7 @@
         </is>
       </c>
       <c r="G20" s="12">
-        <f>COUNTIF($D$27:$D$5000,"Polyvinylchlorid")</f>
+        <f>COUNTIF('Haltungen'!$D$27:$D$5000,"Polyvinylchlorid")</f>
         <v/>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -2914,7 +2924,7 @@
       </c>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="12">
-        <f>COUNTIF($K$27:$K$5000,"Keine")</f>
+        <f>COUNTIF('Haltungen'!$K$27:$K$5000,"Keine")</f>
         <v/>
       </c>
       <c r="K20" s="5" t="n"/>
@@ -2925,7 +2935,7 @@
         </is>
       </c>
       <c r="N20" s="12">
-        <f>COUNTIF($P$27:$P$5000,"Gartenbauer")</f>
+        <f>COUNTIF('Haltungen'!$P$27:$P$5000,"Gartenbauer")</f>
         <v/>
       </c>
       <c r="O20" s="16" t="inlineStr">
@@ -2936,7 +2946,7 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="17">
-        <f>SUMIF($O$27:$O$5000,"Gemeinde",$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Gemeinde",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S20" s="16" t="inlineStr">
@@ -2947,7 +2957,7 @@
       <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="n"/>
       <c r="V20" s="18">
-        <f>SUM($V$27:$V$5000)</f>
+        <f>SUM('Haltungen'!$V$27:$V$5000)</f>
         <v/>
       </c>
       <c r="W20" s="2" t="n"/>
@@ -2964,7 +2974,7 @@
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="12">
-        <f>COUNTIF($J$27:$J$5000,"4")</f>
+        <f>COUNTIF('Haltungen'!$J$27:$J$5000,"4")</f>
         <v/>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -2973,7 +2983,7 @@
         </is>
       </c>
       <c r="E21" s="12">
-        <f>COUNTIF($O$27:$O$5000,"Privat")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Privat")</f>
         <v/>
       </c>
       <c r="F21" s="31" t="inlineStr">
@@ -2982,7 +2992,7 @@
         </is>
       </c>
       <c r="G21" s="12">
-        <f>COUNTIF($D$27:$D$5000,"Polypropylen")</f>
+        <f>COUNTIF('Haltungen'!$D$27:$D$5000,"Polypropylen")</f>
         <v/>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -2996,7 +3006,7 @@
         </is>
       </c>
       <c r="N21" s="12">
-        <f>COUNTA($B$27:$B$5000)-COUNTA($P$27:$P$5000)</f>
+        <f>COUNTA('Haltungen'!$B$27:$B$5000)-COUNTA('Haltungen'!$P$27:$P$5000)</f>
         <v/>
       </c>
       <c r="O21" s="16" t="inlineStr">
@@ -3007,7 +3017,7 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="17">
-        <f>SUMIF($O$27:$O$5000,"Privat",$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Privat",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S21" s="16" t="inlineStr">
@@ -3018,7 +3028,7 @@
       <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="n"/>
       <c r="V21" s="18">
-        <f>SUM($W$27:$W$5000)</f>
+        <f>SUM('Haltungen'!$W$27:$W$5000)</f>
         <v/>
       </c>
       <c r="W21" s="2" t="n"/>
@@ -3039,7 +3049,7 @@
         </is>
       </c>
       <c r="G22" s="12">
-        <f>COUNTA($D$27:$D$5000)-COUNTIF($D$27:$D$5000,"Zement")-COUNTIF($D$27:$D$5000,"Polyethylen")-COUNTIF($D$27:$D$5000,"Beton")-COUNTIF($D$27:$D$5000,"Polyvinylchlorid")-COUNTIF($D$27:$D$5000,"Polypropylen")</f>
+        <f>COUNTA('Haltungen'!$D$27:$D$5000)-COUNTIF('Haltungen'!$D$27:$D$5000,"Zement")-COUNTIF('Haltungen'!$D$27:$D$5000,"Polyethylen")-COUNTIF('Haltungen'!$D$27:$D$5000,"Beton")-COUNTIF('Haltungen'!$D$27:$D$5000,"Polyvinylchlorid")-COUNTIF('Haltungen'!$D$27:$D$5000,"Polypropylen")</f>
         <v/>
       </c>
       <c r="H22" s="5" t="n"/>
@@ -3061,7 +3071,7 @@
       <c r="T22" s="2" t="n"/>
       <c r="U22" s="2" t="n"/>
       <c r="V22" s="18">
-        <f>SUM($X$27:$X$5000)</f>
+        <f>SUM('Haltungen'!$X$27:$X$5000)</f>
         <v/>
       </c>
       <c r="W22" s="2" t="n"/>
@@ -3078,7 +3088,7 @@
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="33">
-        <f>COUNTA($B$27:$B$5000)</f>
+        <f>COUNTA('Haltungen'!$B$27:$B$5000)</f>
         <v/>
       </c>
       <c r="D23" s="34" t="inlineStr">
@@ -3087,7 +3097,7 @@
         </is>
       </c>
       <c r="E23" s="33">
-        <f>COUNTA($O$27:$O$5000)</f>
+        <f>COUNTA('Haltungen'!$O$27:$O$5000)</f>
         <v/>
       </c>
       <c r="F23" s="34" t="inlineStr">
@@ -3096,7 +3106,7 @@
         </is>
       </c>
       <c r="G23" s="33">
-        <f>COUNTA($D$27:$D$5000)</f>
+        <f>COUNTA('Haltungen'!$D$27:$D$5000)</f>
         <v/>
       </c>
       <c r="H23" s="32" t="inlineStr">
@@ -3106,7 +3116,7 @@
       </c>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="33">
-        <f>COUNTA($K$27:$K$5000)</f>
+        <f>COUNTA('Haltungen'!$K$27:$K$5000)</f>
         <v/>
       </c>
       <c r="K23" s="34" t="inlineStr">
@@ -3115,7 +3125,7 @@
         </is>
       </c>
       <c r="L23" s="33">
-        <f>COUNTA($L$27:$L$5000)</f>
+        <f>COUNTA('Haltungen'!$L$27:$L$5000)</f>
         <v/>
       </c>
       <c r="M23" s="34" t="inlineStr">
@@ -3124,7 +3134,7 @@
         </is>
       </c>
       <c r="N23" s="33">
-        <f>COUNTA($B$27:$B$5000)</f>
+        <f>COUNTA('Haltungen'!$B$27:$B$5000)</f>
         <v/>
       </c>
       <c r="O23" s="32" t="inlineStr">
@@ -3135,7 +3145,7 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="35">
-        <f>SUM($N$27:$N$5000)</f>
+        <f>SUM('Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S23" s="16" t="inlineStr">
@@ -3146,7 +3156,7 @@
       <c r="T23" s="2" t="n"/>
       <c r="U23" s="2" t="n"/>
       <c r="V23" s="18">
-        <f>SUM($Y$27:$Y$5000)</f>
+        <f>SUM('Haltungen'!$Y$27:$Y$5000)</f>
         <v/>
       </c>
       <c r="W23" s="2" t="n"/>
@@ -3158,223 +3168,255 @@
         </is>
       </c>
       <c r="AA23" s="33">
-        <f>COUNTA($B$27:$B$5000)</f>
+        <f>COUNTA('Haltungen'!$B$27:$B$5000)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="5" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>Aktuelle Auswahl</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="37">
+        <f>SUBTOTAL(103,$A$27:$A$5000)</f>
+        <v/>
+      </c>
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>Länge m</t>
+        </is>
+      </c>
+      <c r="E24" s="38">
+        <f>SUBTOTAL(109,$G$27:$G$5000)</f>
+        <v/>
+      </c>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="inlineStr">
+        <is>
+          <t>Kosten CHF</t>
+        </is>
+      </c>
+      <c r="H24" s="38">
+        <f>SUBTOTAL(109,$N$27:$N$5000)</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="36" t="inlineStr"/>
-      <c r="B25" s="37" t="n"/>
-      <c r="C25" s="37" t="n"/>
-      <c r="D25" s="37" t="n"/>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="37" t="n"/>
-      <c r="G25" s="37" t="n"/>
-      <c r="H25" s="37" t="n"/>
-      <c r="I25" s="37" t="n"/>
-      <c r="J25" s="37" t="n"/>
-      <c r="K25" s="37" t="n"/>
-      <c r="L25" s="37" t="n"/>
-      <c r="M25" s="37" t="n"/>
-      <c r="N25" s="37" t="n"/>
-      <c r="O25" s="37" t="n"/>
-      <c r="P25" s="37" t="n"/>
-      <c r="Q25" s="37" t="n"/>
-      <c r="R25" s="37" t="n"/>
-      <c r="S25" s="38" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr"/>
+      <c r="B25" s="40" t="n"/>
+      <c r="C25" s="40" t="n"/>
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="40" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="40" t="n"/>
+      <c r="L25" s="40" t="n"/>
+      <c r="M25" s="40" t="n"/>
+      <c r="N25" s="40" t="n"/>
+      <c r="O25" s="40" t="n"/>
+      <c r="P25" s="40" t="n"/>
+      <c r="Q25" s="40" t="n"/>
+      <c r="R25" s="40" t="n"/>
+      <c r="S25" s="41" t="inlineStr">
         <is>
           <t>Ausmass</t>
         </is>
       </c>
-      <c r="T25" s="39" t="n"/>
-      <c r="U25" s="39" t="n"/>
-      <c r="V25" s="39" t="n"/>
-      <c r="W25" s="39" t="n"/>
-      <c r="X25" s="39" t="n"/>
-      <c r="Y25" s="39" t="n"/>
-      <c r="Z25" s="38" t="inlineStr">
+      <c r="T25" s="42" t="n"/>
+      <c r="U25" s="42" t="n"/>
+      <c r="V25" s="42" t="n"/>
+      <c r="W25" s="42" t="n"/>
+      <c r="X25" s="42" t="n"/>
+      <c r="Y25" s="42" t="n"/>
+      <c r="Z25" s="41" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AA25" s="39" t="n"/>
+      <c r="AA25" s="42" t="n"/>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>NR.</t>
         </is>
       </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Haltungsname (ID)</t>
         </is>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>Strasse</t>
         </is>
       </c>
-      <c r="D26" s="40" t="inlineStr">
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t>Rohrmaterial</t>
         </is>
       </c>
-      <c r="E26" s="40" t="inlineStr">
+      <c r="E26" s="43" t="inlineStr">
         <is>
           <t>DN mm</t>
         </is>
       </c>
-      <c r="F26" s="40" t="inlineStr">
+      <c r="F26" s="43" t="inlineStr">
         <is>
           <t>Nutzungsart</t>
         </is>
       </c>
-      <c r="G26" s="40" t="inlineStr">
+      <c r="G26" s="43" t="inlineStr">
         <is>
           <t>Haltungslänge m</t>
         </is>
       </c>
-      <c r="H26" s="40" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
         <is>
           <t>Inspektionsrichtung</t>
         </is>
       </c>
-      <c r="I26" s="40" t="inlineStr">
+      <c r="I26" s="43" t="inlineStr">
         <is>
           <t>Primäre Schäden</t>
         </is>
       </c>
-      <c r="J26" s="40" t="inlineStr">
+      <c r="J26" s="43" t="inlineStr">
         <is>
           <t>Zustandsklasse</t>
         </is>
       </c>
-      <c r="K26" s="40" t="inlineStr">
+      <c r="K26" s="43" t="inlineStr">
         <is>
           <t>Prüfungsresultat</t>
         </is>
       </c>
-      <c r="L26" s="40" t="inlineStr">
+      <c r="L26" s="43" t="inlineStr">
         <is>
           <t>Sanieren Ja/Nein</t>
         </is>
       </c>
-      <c r="M26" s="40" t="inlineStr">
+      <c r="M26" s="43" t="inlineStr">
         <is>
           <t>Empfohlene Sanierungsmassnahmen</t>
         </is>
       </c>
-      <c r="N26" s="40" t="inlineStr">
+      <c r="N26" s="43" t="inlineStr">
         <is>
           <t>Kosten</t>
         </is>
       </c>
-      <c r="O26" s="40" t="inlineStr">
+      <c r="O26" s="43" t="inlineStr">
         <is>
           <t>Eigentümer</t>
         </is>
       </c>
-      <c r="P26" s="40" t="inlineStr">
+      <c r="P26" s="43" t="inlineStr">
         <is>
           <t>Ausgeführt durch</t>
         </is>
       </c>
-      <c r="Q26" s="40" t="inlineStr">
+      <c r="Q26" s="43" t="inlineStr">
         <is>
           <t>Bemerkungen</t>
         </is>
       </c>
-      <c r="R26" s="40" t="inlineStr">
+      <c r="R26" s="43" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="S26" s="40" t="inlineStr">
+      <c r="S26" s="43" t="inlineStr">
         <is>
           <t>Renovierung Inliner Stk.</t>
         </is>
       </c>
-      <c r="T26" s="40" t="inlineStr">
+      <c r="T26" s="43" t="inlineStr">
         <is>
           <t>Renovierung Inliner m</t>
         </is>
       </c>
-      <c r="U26" s="40" t="inlineStr">
+      <c r="U26" s="43" t="inlineStr">
         <is>
           <t>Anschlüsse verpressen</t>
         </is>
       </c>
-      <c r="V26" s="40" t="inlineStr">
+      <c r="V26" s="43" t="inlineStr">
         <is>
           <t>Reparatur Manschette</t>
         </is>
       </c>
-      <c r="W26" s="40" t="inlineStr">
+      <c r="W26" s="43" t="inlineStr">
         <is>
           <t>Linerendmanschette LEM</t>
         </is>
       </c>
-      <c r="X26" s="40" t="inlineStr">
+      <c r="X26" s="43" t="inlineStr">
         <is>
           <t>Reparatur Kurzliner</t>
         </is>
       </c>
-      <c r="Y26" s="40" t="inlineStr">
+      <c r="Y26" s="43" t="inlineStr">
         <is>
           <t>Erneuerung Neubau m</t>
         </is>
       </c>
-      <c r="Z26" s="40" t="inlineStr">
+      <c r="Z26" s="43" t="inlineStr">
         <is>
           <t>offen/abgeschlossen</t>
         </is>
       </c>
-      <c r="AA26" s="40" t="inlineStr">
+      <c r="AA26" s="43" t="inlineStr">
         <is>
           <t>Datum/Jahr</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="41" t="n"/>
-      <c r="B27" s="42" t="n"/>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="43" t="n"/>
-      <c r="F27" s="42" t="n"/>
-      <c r="G27" s="44" t="n"/>
-      <c r="H27" s="42" t="n"/>
-      <c r="I27" s="45" t="n"/>
-      <c r="J27" s="41" t="n"/>
-      <c r="K27" s="41" t="n"/>
-      <c r="L27" s="41" t="n"/>
-      <c r="M27" s="45" t="n"/>
-      <c r="N27" s="46" t="n"/>
-      <c r="O27" s="41" t="n"/>
-      <c r="P27" s="41" t="n"/>
-      <c r="Q27" s="45" t="n"/>
-      <c r="R27" s="47" t="n"/>
-      <c r="S27" s="48" t="n"/>
-      <c r="T27" s="44" t="n"/>
-      <c r="U27" s="48" t="n"/>
-      <c r="V27" s="48" t="n"/>
-      <c r="W27" s="48" t="n"/>
-      <c r="X27" s="48" t="n"/>
-      <c r="Y27" s="44" t="n"/>
-      <c r="Z27" s="41" t="n"/>
-      <c r="AA27" s="41" t="n"/>
+      <c r="A27" s="44" t="n"/>
+      <c r="B27" s="45" t="n"/>
+      <c r="C27" s="45" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="46" t="n"/>
+      <c r="F27" s="45" t="n"/>
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="45" t="n"/>
+      <c r="I27" s="48" t="n"/>
+      <c r="J27" s="44" t="n"/>
+      <c r="K27" s="44" t="n"/>
+      <c r="L27" s="44" t="n"/>
+      <c r="M27" s="48" t="n"/>
+      <c r="N27" s="49" t="n"/>
+      <c r="O27" s="44" t="n"/>
+      <c r="P27" s="44" t="n"/>
+      <c r="Q27" s="48" t="n"/>
+      <c r="R27" s="50" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="47" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="51" t="n"/>
+      <c r="W27" s="51" t="n"/>
+      <c r="X27" s="51" t="n"/>
+      <c r="Y27" s="47" t="n"/>
+      <c r="Z27" s="44" t="n"/>
+      <c r="AA27" s="44" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A26:AA5000"/>
-  <mergeCells count="48">
+  <mergeCells count="50">
     <mergeCell ref="K16:L16"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A25:R25"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="S23:U23"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="V22:Y22"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="O21:Q21"/>
@@ -3540,7 +3582,7 @@
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/Export_Vorlage/Haltungen.xlsx
+++ b/Export_Vorlage/Haltungen.xlsx
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="E17" s="12">
-        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Abwasser Uri")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Abwasser Uri")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU_von_oeffentlich")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU_von_oeffentlich (Abwasserverband)")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU_von_privat")+COUNTIF('Haltungen'!$O$27:$O$5000,"AWU_von_privat (Abwasserverband)")</f>
         <v/>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -2684,7 +2684,7 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="17">
-        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Abwasser Uri",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU",'Haltungen'!$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Abwasser Uri",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU_von_oeffentlich",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU_von_oeffentlich (Abwasserverband)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU_von_privat",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"AWU_von_privat (Abwasserverband)",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S17" s="16" t="inlineStr">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E18" s="12">
-        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton Uri")+COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton Uri")+COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton")+COUNTIF('Haltungen'!$O$27:$O$5000,"Kanton Uri (Kanton)")</f>
         <v/>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -2776,7 +2776,7 @@
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="17">
-        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Kanton Uri",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Kanton",'Haltungen'!$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Kanton Uri",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Kanton",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Kanton Uri (Kanton)",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S18" s="16" t="inlineStr">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="E19" s="12">
-        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Bund")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Bund")+COUNTIF('Haltungen'!$O$27:$O$5000,"Bund Astra")+COUNTIF('Haltungen'!$O$27:$O$5000,"Bund Astra (Bund)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Bund (Bund)")</f>
         <v/>
       </c>
       <c r="F19" s="26" t="inlineStr">
@@ -2861,7 +2861,7 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="17">
-        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Bund",'Haltungen'!$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Bund",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Bund Astra",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Bund Astra (Bund)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Bund (Bund)",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S19" s="16" t="inlineStr">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="E20" s="12">
-        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Gemeinde")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Gemeinde")+COUNTIF('Haltungen'!$O$27:$O$5000,"Altdorf")+COUNTIF('Haltungen'!$O$27:$O$5000,"Altdorf (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Bürglen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Bürglen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Schattdorf")+COUNTIF('Haltungen'!$O$27:$O$5000,"Schattdorf (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Andermatt")+COUNTIF('Haltungen'!$O$27:$O$5000,"Andermatt (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Attinghausen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Attinghausen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Erstfeld")+COUNTIF('Haltungen'!$O$27:$O$5000,"Erstfeld (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Flüelen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Flüelen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Göschenen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Göschenen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Gurtnellen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Gurtnellen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Hospental")+COUNTIF('Haltungen'!$O$27:$O$5000,"Hospental (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Isenthal")+COUNTIF('Haltungen'!$O$27:$O$5000,"Isenthal (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Realp")+COUNTIF('Haltungen'!$O$27:$O$5000,"Realp (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Seedorf")+COUNTIF('Haltungen'!$O$27:$O$5000,"Seedorf (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Seelisberg")+COUNTIF('Haltungen'!$O$27:$O$5000,"Seelisberg (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Silenen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Silenen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Sisikon")+COUNTIF('Haltungen'!$O$27:$O$5000,"Sisikon (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Spiringen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Spiringen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Unterschächen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Unterschächen (Gemeinde)")+COUNTIF('Haltungen'!$O$27:$O$5000,"Wassen")+COUNTIF('Haltungen'!$O$27:$O$5000,"Wassen (Gemeinde)")</f>
         <v/>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="17">
-        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Gemeinde",'Haltungen'!$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Gemeinde",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Altdorf",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Altdorf (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Bürglen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Bürglen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Schattdorf",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Schattdorf (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Andermatt",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Andermatt (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Attinghausen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Attinghausen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Erstfeld",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Erstfeld (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Flüelen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Flüelen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Göschenen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Göschenen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Gurtnellen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Gurtnellen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Hospental",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Hospental (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Isenthal",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Isenthal (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Realp",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Realp (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Seedorf",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Seedorf (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Seelisberg",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Seelisberg (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Silenen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Silenen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Sisikon",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Sisikon (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Spiringen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Spiringen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Unterschächen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Unterschächen (Gemeinde)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Wassen",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Wassen (Gemeinde)",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S20" s="16" t="inlineStr">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="E21" s="12">
-        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Privat")</f>
+        <f>COUNTIF('Haltungen'!$O$27:$O$5000,"Privat")+COUNTIF('Haltungen'!$O$27:$O$5000,"Privat (Privat)")+COUNTIF('Haltungen'!$O$27:$O$5000,"RUAG")+COUNTIF('Haltungen'!$O$27:$O$5000,"RUAG (Privat)")</f>
         <v/>
       </c>
       <c r="F21" s="31" t="inlineStr">
@@ -3017,7 +3017,7 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="17">
-        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Privat",'Haltungen'!$N$27:$N$5000)</f>
+        <f>SUMIF('Haltungen'!$O$27:$O$5000,"Privat",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"Privat (Privat)",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"RUAG",'Haltungen'!$N$27:$N$5000)+SUMIF('Haltungen'!$O$27:$O$5000,"RUAG (Privat)",'Haltungen'!$N$27:$N$5000)</f>
         <v/>
       </c>
       <c r="S21" s="16" t="inlineStr">
@@ -3552,32 +3552,179 @@
     <cfRule type="expression" priority="27" dxfId="0" stopIfTrue="1">
       <formula>$O27="AWU"</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="28" dxfId="0" stopIfTrue="1">
+      <formula>$O27="AWU_von_oeffentlich"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="0" stopIfTrue="1">
+      <formula>$O27="AWU_von_oeffentlich (Abwasserverband)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="0" stopIfTrue="1">
+      <formula>$O27="AWU_von_privat"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" dxfId="0" stopIfTrue="1">
+      <formula>$O27="AWU_von_privat (Abwasserverband)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="6" stopIfTrue="1">
       <formula>$O27="Kanton Uri"</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" dxfId="6" stopIfTrue="1">
+    <cfRule type="expression" priority="33" dxfId="6" stopIfTrue="1">
       <formula>$O27="Kanton"</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" dxfId="10" stopIfTrue="1">
+    <cfRule type="expression" priority="34" dxfId="6" stopIfTrue="1">
+      <formula>$O27="Kanton Uri (Kanton)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="10" stopIfTrue="1">
       <formula>$O27="Bund"</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="36" dxfId="10" stopIfTrue="1">
+      <formula>$O27="Bund Astra"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="37" dxfId="10" stopIfTrue="1">
+      <formula>$O27="Bund Astra (Bund)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" dxfId="10" stopIfTrue="1">
+      <formula>$O27="Bund (Bund)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" dxfId="2" stopIfTrue="1">
       <formula>$O27="Gemeinde"</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="40" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Altdorf"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="41" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Altdorf (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Bürglen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="43" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Bürglen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="44" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Schattdorf"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Schattdorf (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="46" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Andermatt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="47" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Andermatt (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Attinghausen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="49" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Attinghausen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="50" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Erstfeld"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="51" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Erstfeld (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="52" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Flüelen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="53" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Flüelen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Göschenen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="55" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Göschenen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="56" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Gurtnellen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="57" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Gurtnellen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="58" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Hospental"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="59" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Hospental (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Isenthal"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="61" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Isenthal (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="62" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Realp"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Realp (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="64" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Seedorf"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="65" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Seedorf (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Seelisberg"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="67" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Seelisberg (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="68" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Silenen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="69" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Silenen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="70" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Sisikon"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="71" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Sisikon (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="72" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Spiringen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="73" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Spiringen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="74" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Unterschächen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="75" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Unterschächen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="76" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Wassen"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="77" dxfId="2" stopIfTrue="1">
+      <formula>$O27="Wassen (Gemeinde)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="78" dxfId="4" stopIfTrue="1">
       <formula>$O27="Privat"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="79" dxfId="4" stopIfTrue="1">
+      <formula>$O27="Privat (Privat)"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="80" dxfId="4" stopIfTrue="1">
+      <formula>$O27="RUAG"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="81" dxfId="4" stopIfTrue="1">
+      <formula>$O27="RUAG (Privat)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z27:Z5000">
-    <cfRule type="expression" priority="33" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="82" dxfId="4" stopIfTrue="1">
       <formula>$Z27="offen"</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="11" stopIfTrue="1">
+    <cfRule type="expression" priority="83" dxfId="11" stopIfTrue="1">
       <formula>$Z27="abgeschlossen"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:AA5000">
-    <cfRule type="expression" priority="35" dxfId="12">
+    <cfRule type="expression" priority="84" dxfId="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
